--- a/contractor_forms/017_tree_trimming_request_form--contractor_forms.xlsx
+++ b/contractor_forms/017_tree_trimming_request_form--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1073,8 +1073,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'tree_trimming'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Trimming'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'tree_pruning'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Pruning'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'tree_removal'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Removal'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'tree_cutting'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Cutting'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'tree_shaping'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Shaping'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'tree_pruning'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Pruning'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'tree_chopping'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Chopping'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'tree_cutting'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Tree Cutting'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'small'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Small'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'large'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Large'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'10-20_ft'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': '10-20 ft'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'20-50_ft'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': '20-50 ft'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'50-100_ft'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': '50-100 ft'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
